--- a/server/src/data/西班牙语单词本-副词.xlsx
+++ b/server/src/data/西班牙语单词本-副词.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的项目\业务mvp\vocabulario-espanol\server\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2655ADAF-D5CD-4918-A311-FC53BBEB6B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BD7236-8035-4AC7-8934-4FE05DC4864B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31635" yWindow="2310" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34110" yWindow="1635" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="副词表" sheetId="5" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="228">
   <si>
     <t>原形</t>
   </si>
@@ -51,13 +51,13 @@
     <t>不管怎样</t>
   </si>
   <si>
-    <t>De cualquier manera（原形）</t>
-  </si>
-  <si>
-    <t>不管怎样，她看着我的时候看到的是完整的我</t>
-  </si>
-  <si>
-    <t>De cualquier manera, cuando me mira me ve entero</t>
+    <t>De cualquier manera（原形） | 比较级: más De cualquier manera | 最高级: lo más De cualquier manera</t>
+  </si>
+  <si>
+    <t>不管怎样，她看着我的时候看到的是完整的我。</t>
+  </si>
+  <si>
+    <t>Él De cualquier manera, cuando me mira me ve entero.</t>
   </si>
   <si>
     <t>副词短语，用于句首/句中，表让步</t>
@@ -69,16 +69,13 @@
     <t>任何情况下</t>
   </si>
   <si>
-    <t>En cualquier caso（原形）</t>
-  </si>
-  <si>
-    <t>任何情况下，她抓住我的手时，她的手还是暖的</t>
-  </si>
-  <si>
-    <t>En cualquier caso, su mano sigue caliente cuando agarra la mía</t>
-  </si>
-  <si>
-    <t>副词短语，用于句首/句中，表让步</t>
+    <t>En cualquier caso（原形） | 比较级: más En cualquier caso | 最高级: lo más En cualquier caso</t>
+  </si>
+  <si>
+    <t>任何情况下，她抓住我的手时，她的手还是暖的。</t>
+  </si>
+  <si>
+    <t>Él En cualquier caso, su mano sigue caliente cuando agarra la mía.</t>
   </si>
   <si>
     <t>Pase lo que pase</t>
@@ -87,13 +84,13 @@
     <t>无论发生什么</t>
   </si>
   <si>
-    <t>Pase lo que pase（原形）</t>
-  </si>
-  <si>
-    <t>无论发生什么，她几十年来都是我的家</t>
-  </si>
-  <si>
-    <t>Pase lo que pase, ella es mi casa hace décadas</t>
+    <t>Pase lo que pase（原形） | 比较级: más Pase lo que pase | 最高级: lo más Pase lo que pase</t>
+  </si>
+  <si>
+    <t>无论发生什么，她几十年来都是我的家。</t>
+  </si>
+  <si>
+    <t>Él Pase lo que pase, ella es mi casa hace décadas.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表让步，虚拟式用法</t>
@@ -105,13 +102,13 @@
     <t>例如</t>
   </si>
   <si>
-    <t>Por ejemplo（原形）</t>
-  </si>
-  <si>
-    <t>比如有些人看到浪漫，有些人看到孤独</t>
-  </si>
-  <si>
-    <t>Por ejemplo, unos ven romanticismo, otros ven soledad</t>
+    <t>Por ejemplo（原形） | 比较级: más Por ejemplo | 最高级: lo más Por ejemplo</t>
+  </si>
+  <si>
+    <t>他比如有些人看到浪漫，有些人看到孤独。</t>
+  </si>
+  <si>
+    <t>Él Por ejemplo, unos ven romanticismo, otros ven soledad.</t>
   </si>
   <si>
     <t>副词短语，用于句首/句中，表举例</t>
@@ -123,13 +120,13 @@
     <t>这样</t>
   </si>
   <si>
-    <t>así（原形）</t>
-  </si>
-  <si>
-    <t>我就这样看着它，什么也不说</t>
-  </si>
-  <si>
-    <t>Yo así la miro nomás, sin ponerle palabra</t>
+    <t>así（原形） | 比较级: más Asi | 最高级: lo más Asi</t>
+  </si>
+  <si>
+    <t>我就这样看着它，什么也不说。</t>
+  </si>
+  <si>
+    <t>Él Yo así la miro nomás, sin ponerle palabra.</t>
   </si>
   <si>
     <t>副词，修饰动词/形容词，表方式</t>
@@ -141,16 +138,13 @@
     <t>无论如何</t>
   </si>
   <si>
-    <t>De todas formas（原形）</t>
-  </si>
-  <si>
-    <t>无论如何，月亮没变，只是我们用各自的心情去装饰它</t>
-  </si>
-  <si>
-    <t>De todas formas, la luna no cambia, solo nosotros la vestimos de lo que sentimos</t>
-  </si>
-  <si>
-    <t>副词短语，用于句首/句中，表让步</t>
+    <t>De todas formas（原形） | 比较级: más De todas formas | 最高级: lo más De todas formas</t>
+  </si>
+  <si>
+    <t>无论如何，月亮没变，只是我们用各自的心情去装饰它。</t>
+  </si>
+  <si>
+    <t>Él De todas formas, la luna no cambia, solo nosotros la vestimos de lo que sentimos.</t>
   </si>
   <si>
     <t>Ni siquiera</t>
@@ -159,13 +153,13 @@
     <t>甚至不</t>
   </si>
   <si>
-    <t>Ni siquiera（原形）</t>
-  </si>
-  <si>
-    <t>我甚至没接</t>
-  </si>
-  <si>
-    <t>ni siquiera conteste</t>
+    <t>Ni siquiera（原形） | 比较级: más Ni siquiera | 最高级: lo más Ni siquiera</t>
+  </si>
+  <si>
+    <t>我甚至没接。</t>
+  </si>
+  <si>
+    <t>Él ni siquiera conteste.</t>
   </si>
   <si>
     <t>副词短语，用于句中，表递进否定</t>
@@ -177,13 +171,13 @@
     <t>而是,宁可</t>
   </si>
   <si>
-    <t>más bien（原形）</t>
-  </si>
-  <si>
-    <t>不是因为生气，而是因为我在睡午觉</t>
-  </si>
-  <si>
-    <t>No fue por enojo, más bien porque estaba durmiendo la siesta</t>
+    <t>más bien（原形） | 比较级: más Mas bien | 最高级: lo más Mas bien</t>
+  </si>
+  <si>
+    <t>不是因为生气，而是因为我在睡午觉。</t>
+  </si>
+  <si>
+    <t>Él No fue por enojo, más bien porque estaba durmiendo la siesta.</t>
   </si>
   <si>
     <t>副词短语，用于句中，表转折</t>
@@ -195,13 +189,13 @@
     <t>更确切地说</t>
   </si>
   <si>
-    <t>Mejor dicho（原形）</t>
-  </si>
-  <si>
-    <t>更确切地说，我瘫在沙发上，手机开着震动，完全没感觉到</t>
-  </si>
-  <si>
-    <t>Mejor dicho, estaba tirado en el sillón con el celular en vibrador y no lo senti</t>
+    <t>Mejor dicho（原形） | 比较级: más Mejor dicho | 最高级: lo más Mejor dicho</t>
+  </si>
+  <si>
+    <t>更确切地说，我瘫在沙发上，手机开着震动，完全没感觉到。</t>
+  </si>
+  <si>
+    <t>Él Mejor dicho, estaba tirado en el sillón con el celular en vibrador y no lo senti.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表修正说明</t>
@@ -213,13 +207,13 @@
     <t>行,好</t>
   </si>
   <si>
-    <t>Vale（原形）</t>
-  </si>
-  <si>
-    <t>行，有一点</t>
-  </si>
-  <si>
-    <t>Vale, un poco</t>
+    <t>Vale（原形） | 比较级: más Vale | 最高级: lo más Vale</t>
+  </si>
+  <si>
+    <t>他行，有一点。</t>
+  </si>
+  <si>
+    <t>Él Vale, un poco.</t>
   </si>
   <si>
     <t>感叹词/副词，用于口语，表同意</t>
@@ -231,13 +225,13 @@
     <t>当然可以</t>
   </si>
   <si>
-    <t>Claro que sí（原形）</t>
-  </si>
-  <si>
-    <t>当然可以，哪怕只是喝着马黛茶看看海</t>
-  </si>
-  <si>
-    <t>Claro que si, aunque sea con un mate y mirando el mar</t>
+    <t>Claro que sí（原形） | 比较级: más Claro que sí | 最高级: lo más Claro que sí</t>
+  </si>
+  <si>
+    <t>他当然可以，哪怕只是喝着马黛茶看看海。</t>
+  </si>
+  <si>
+    <t>Él Claro que si, aunque sea con un mate y mirando el mar.</t>
   </si>
   <si>
     <t>副词短语，用于口语，表肯定回答</t>
@@ -249,13 +243,13 @@
     <t>当然不</t>
   </si>
   <si>
-    <t>Claro que no（原形）</t>
-  </si>
-  <si>
-    <t>当然不，那更糟</t>
-  </si>
-  <si>
-    <t>Claro gue no, eso es peor</t>
+    <t>Claro que no（原形） | 比较级: más Claro que no | 最高级: lo más Claro que no</t>
+  </si>
+  <si>
+    <t>他当然不，那更糟。</t>
+  </si>
+  <si>
+    <t>Él Claro gue no, eso es peor.</t>
   </si>
   <si>
     <t>副词短语，用于口语，表否定回答</t>
@@ -267,13 +261,13 @@
     <t>从头到尾</t>
   </si>
   <si>
-    <t>De cabo a rabo（原形）</t>
-  </si>
-  <si>
-    <t>我一晚上从头到尾读完了那本小说</t>
-  </si>
-  <si>
-    <t>Me leí la novela de cabo a rabo en una noche</t>
+    <t>De cabo a rabo（原形） | 比较级: más De cabo a rabo | 最高级: lo más De cabo a rabo</t>
+  </si>
+  <si>
+    <t>我一晚上从头到尾读完了那本小说。</t>
+  </si>
+  <si>
+    <t>Él Me leí la novela de cabo a rabo en una noche.</t>
   </si>
   <si>
     <t>副词短语，修饰动词，表全程</t>
@@ -285,13 +279,13 @@
     <t>以防万一</t>
   </si>
   <si>
-    <t>Por si acaso（原形）</t>
-  </si>
-  <si>
-    <t>以防万一，我把我最喜欢的那些页拍了下来</t>
-  </si>
-  <si>
-    <t>Por si acaso, le saque fotos a las paginas que más me gustaron</t>
+    <t>Por si acaso（原形） | 比较级: más Por si acaso | 最高级: lo más Por si acaso</t>
+  </si>
+  <si>
+    <t>以防万一，我把我最喜欢的那些页拍了下来。</t>
+  </si>
+  <si>
+    <t>Él Por si acaso, le saque fotos a las paginas que más me gustaron.</t>
   </si>
   <si>
     <t>副词短语，用于句首/句中，表目的</t>
@@ -303,13 +297,13 @@
     <t>非常情愿地</t>
   </si>
   <si>
-    <t>De mil amores（原形）</t>
-  </si>
-  <si>
-    <t>你要是让我再读一遍，我会十分乐意</t>
-  </si>
-  <si>
-    <t>Si me pidieras que la vuelva a leer, lo haria de mil amores</t>
+    <t>De mil amores（原形） | 比较级: más De mil amores | 最高级: lo más De mil amores</t>
+  </si>
+  <si>
+    <t>你要是让我再读一遍，我会十分乐意。</t>
+  </si>
+  <si>
+    <t>Él Si me pidieras que la vuelva a leer, lo haria de mil amores.</t>
   </si>
   <si>
     <t>副词短语，修饰动词，表乐意</t>
@@ -321,13 +315,13 @@
     <t>一次性/干脆</t>
   </si>
   <si>
-    <t>De una vez（原形）</t>
-  </si>
-  <si>
-    <t>算了，我干脆下周六搬家</t>
-  </si>
-  <si>
-    <t>Ya fue, me mudo de una vez el sabado que viene</t>
+    <t>De una vez（原形） | 比较级: más De una vez | 最高级: lo más De una vez</t>
+  </si>
+  <si>
+    <t>算了，我干脆下周六搬家。</t>
+  </si>
+  <si>
+    <t>Él Ya fue, me mudo de una vez el sabado que viene.</t>
   </si>
   <si>
     <t>副词短语，修饰动词，表方式</t>
@@ -339,13 +333,13 @@
     <t>预先,事先</t>
   </si>
   <si>
-    <t>De antemano（原形）</t>
-  </si>
-  <si>
-    <t>我事先跟你说好，搬箱子我需要帮忙</t>
-  </si>
-  <si>
-    <t>Te aviso de antemano que voy a necesitar ayuda con las cajas</t>
+    <t>De antemano（原形） | 比较级: más De antemano | 最高级: lo más De antemano</t>
+  </si>
+  <si>
+    <t>我事先跟你说好，搬箱子我需要帮忙。</t>
+  </si>
+  <si>
+    <t>Él Te aviso de antemano que voy a necesitar ayuda con las cajas.</t>
   </si>
   <si>
     <t>副词短语，修饰动词，表时间</t>
@@ -357,13 +351,13 @@
     <t>半开玩笑半认真地</t>
   </si>
   <si>
-    <t>Entre bromas y veras（原形）</t>
-  </si>
-  <si>
-    <t>半开玩笑半认真地说，如果新家出现一只蟑螂，我就去住酒店</t>
-  </si>
-  <si>
-    <t>Entre bromas y veras, si veo una cucaracha en el departamento nuevo, me voy a vivir a un hotel</t>
+    <t>Entre bromas y veras（原形） | 比较级: más Entre bromas y veras | 最高级: lo más Entre bromas y veras</t>
+  </si>
+  <si>
+    <t>半开玩笑半认真地说，如果新家出现一只蟑螂，我就去住酒店。</t>
+  </si>
+  <si>
+    <t>Él Entre bromas y veras, si veo una cucaracha en el departamento nuevo, me voy a vivir a un hotel.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表方式</t>
@@ -375,13 +369,13 @@
     <t>凭经验</t>
   </si>
   <si>
-    <t>Por experiencia（原形）</t>
-  </si>
-  <si>
-    <t>凭经验我知道汤还要过一会儿才有味道</t>
-  </si>
-  <si>
-    <t>Por experiencia sé que falta un rato para que la sopa tenga gusto</t>
+    <t>Por experiencia（原形） | 比较级: más Por experiencia | 最高级: lo más Por experiencia</t>
+  </si>
+  <si>
+    <t>凭经验我知道汤还要过一会儿才有味道。</t>
+  </si>
+  <si>
+    <t>Él Por experiencia sé que falta un rato para que la sopa tenga gusto.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表依据</t>
@@ -393,13 +387,13 @@
     <t>一眼看去</t>
   </si>
   <si>
-    <t>A simple vista（原形）</t>
-  </si>
-  <si>
-    <t>一眼看去，水已经开了</t>
-  </si>
-  <si>
-    <t>A simple vista el agua ya está hirviendo</t>
+    <t>A simple vista（原形） | 比较级: más A simple vista | 最高级: lo más A simple vista</t>
+  </si>
+  <si>
+    <t>他一眼看去，水已经开了。</t>
+  </si>
+  <si>
+    <t>Él A simple vista el agua ya está hirviendo.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表判断</t>
@@ -411,13 +405,13 @@
     <t>不再多说</t>
   </si>
   <si>
-    <t>Sin más（原形）</t>
-  </si>
-  <si>
-    <t>不再多说，我放了盐，盖上锅盖，让它自己慢慢煮</t>
-  </si>
-  <si>
-    <t>Sin mas, le pongo sal, tapo la olla y dejo que haga lo suyo</t>
+    <t>Sin más（原形） | 比较级: más Sin más | 最高级: lo más Sin más</t>
+  </si>
+  <si>
+    <t>不再多说，我放了盐，盖上锅盖，让它自己慢慢煮。</t>
+  </si>
+  <si>
+    <t>Él Sin mas, le pongo sal, tapo la olla y dejo que haga lo suyo.</t>
   </si>
   <si>
     <t>副词短语，用于句首，表承接</t>
@@ -429,13 +423,13 @@
     <t>昨天</t>
   </si>
   <si>
-    <t>Ayer（原形）</t>
-  </si>
-  <si>
-    <t>昨日的负担，我已轻轻卸下</t>
-  </si>
-  <si>
-    <t>Ayer dejé ir suavemente las cargas</t>
+    <t>Ayer（原形） | 比较级: más Ayer | 最高级: lo más Ayer</t>
+  </si>
+  <si>
+    <t>昨日的负担，我已轻轻卸下。</t>
+  </si>
+  <si>
+    <t>Él Ayer dejé ir suavemente las cargas.</t>
   </si>
   <si>
     <t>时间副词，用于句首/句末</t>
@@ -447,16 +441,13 @@
     <t>今天</t>
   </si>
   <si>
-    <t>Hoy（原形）</t>
-  </si>
-  <si>
-    <t>今日的风景，我正深深珍惜</t>
-  </si>
-  <si>
-    <t>Hoy, valoro profundamente este instante</t>
-  </si>
-  <si>
-    <t>时间副词，用于句首/句末</t>
+    <t>Hoy（原形） | 比较级: más Hoy | 最高级: lo más Hoy</t>
+  </si>
+  <si>
+    <t>今日的风景，我正深深珍惜。</t>
+  </si>
+  <si>
+    <t>Él Hoy, valoro profundamente este instante.</t>
   </si>
   <si>
     <t>Manana</t>
@@ -465,16 +456,13 @@
     <t>明天</t>
   </si>
   <si>
-    <t>Mañana（原形）</t>
-  </si>
-  <si>
-    <t>明日的希望，我将静静期待</t>
-  </si>
-  <si>
-    <t>Manana espero con calma la promesa</t>
-  </si>
-  <si>
-    <t>时间副词，用于句首/句末</t>
+    <t>Mañana（原形） | 比较级: más Manana | 最高级: lo más Manana</t>
+  </si>
+  <si>
+    <t>明日的希望，我将静静期待。</t>
+  </si>
+  <si>
+    <t>Él Manana espero con calma la promesa.</t>
   </si>
   <si>
     <t>Temprano</t>
@@ -483,13 +471,13 @@
     <t>早</t>
   </si>
   <si>
-    <t>Temprano（原形）</t>
-  </si>
-  <si>
-    <t>有人早早开始奔向未来</t>
-  </si>
-  <si>
-    <t>Algunos empiezan temprano a correr hacia el futuro</t>
+    <t>Temprano（原形） | 比较级: más Temprano | 最高级: lo más Temprano</t>
+  </si>
+  <si>
+    <t>他有人早早开始奔向未来。</t>
+  </si>
+  <si>
+    <t>Él Algunos empiezan temprano a correr hacia el futuro.</t>
   </si>
   <si>
     <t>时间副词，修饰动词</t>
@@ -501,16 +489,13 @@
     <t>立即</t>
   </si>
   <si>
-    <t>Enseguida（原形）</t>
-  </si>
-  <si>
-    <t>有人在领悟真相后立即改变</t>
-  </si>
-  <si>
-    <t>otros deciden cambiar enseguida al comprender la verdad</t>
-  </si>
-  <si>
-    <t>时间副词，修饰动词</t>
+    <t>Enseguida（原形） | 比较级: más Enseguida | 最高级: lo más Enseguida</t>
+  </si>
+  <si>
+    <t>他有人在领悟真相后立即改变。</t>
+  </si>
+  <si>
+    <t>Él otros deciden cambiar enseguida al comprender la verdad.</t>
   </si>
   <si>
     <t>Mientras</t>
@@ -519,13 +504,13 @@
     <t>同时</t>
   </si>
   <si>
-    <t>Mientras（原形）</t>
-  </si>
-  <si>
-    <t>而与此同时，生命揭示出它的秘密</t>
-  </si>
-  <si>
-    <t>Mientras tanto, la vida revela su secreto</t>
+    <t>Mientras（原形） | 比较级: más Mientras | 最高级: lo más Mientras</t>
+  </si>
+  <si>
+    <t>而与此同时，生命揭示出它的秘密。</t>
+  </si>
+  <si>
+    <t>Él Mientras tanto, la vida revela su secreto.</t>
   </si>
   <si>
     <t>时间副词/连词，表同时</t>
@@ -537,13 +522,13 @@
     <t>从不</t>
   </si>
   <si>
-    <t>Jamás（原形）</t>
-  </si>
-  <si>
-    <t>莫言为时已晚，因为重新开始永远不晚</t>
-  </si>
-  <si>
-    <t>No digas que es demasiado tarde, pues es jamas tarde para comenzar de nuevo</t>
+    <t>Jamás（原形） | 比较级: más Jamás | 最高级: lo más Jamás</t>
+  </si>
+  <si>
+    <t>他莫言为时已晚，因为重新开始永远不晚。</t>
+  </si>
+  <si>
+    <t>Él No digas que es demasiado tarde, pues es jamas tarde para comenzar de nuevo.</t>
   </si>
   <si>
     <t>否定副词，用于句中，比nunca语气更强</t>
@@ -555,13 +540,13 @@
     <t>很快</t>
   </si>
   <si>
-    <t>Pronto（原形）</t>
-  </si>
-  <si>
-    <t>你所渴望的改变很快就会到来</t>
-  </si>
-  <si>
-    <t>El cambio que anhelas llegara pronto</t>
+    <t>Pronto（原形） | 比较级: más Pronto | 最高级: lo más Pronto</t>
+  </si>
+  <si>
+    <t>你所渴望的改变很快就会到来。</t>
+  </si>
+  <si>
+    <t>El cambio que anhelas llegara pronto.</t>
   </si>
   <si>
     <t>时间副词，用于句末/句首</t>
@@ -573,16 +558,13 @@
     <t>晚</t>
   </si>
   <si>
-    <t>Tarde（原形）</t>
-  </si>
-  <si>
-    <t>莫言为时已晚</t>
-  </si>
-  <si>
-    <t>No digas que es demasiado tarde</t>
-  </si>
-  <si>
-    <t>时间副词，用于句末/句首</t>
+    <t>Tarde（原形） | 比较级: más Tarde | 最高级: lo más Tarde</t>
+  </si>
+  <si>
+    <t>他莫言为时已晚。</t>
+  </si>
+  <si>
+    <t>Él No digas que es demasiado tarde.</t>
   </si>
   <si>
     <t>Aún</t>
@@ -591,13 +573,13 @@
     <t>仍然</t>
   </si>
   <si>
-    <t>Aún（原形）</t>
-  </si>
-  <si>
-    <t>心灵总是珍藏着一隅希望，即使在最深沉的黑夜</t>
-  </si>
-  <si>
-    <t>El corazón siempre guarda un rincón de esperanza, aún en las noches más oscuras</t>
+    <t>Aún（原形） | 比较级: más Aún | 最高级: lo más Aún</t>
+  </si>
+  <si>
+    <t>他心灵总是珍藏着一隅希望，即使在最深沉的黑夜。</t>
+  </si>
+  <si>
+    <t>El corazón siempre guarda un rincón de esperanza, aún en las noches más oscuras.</t>
   </si>
   <si>
     <t>副词，用于句中，表仍然</t>
@@ -609,13 +591,13 @@
     <t>总是</t>
   </si>
   <si>
-    <t>Siempre（原形）</t>
-  </si>
-  <si>
-    <t>心灵总是珍藏着一隅希望</t>
-  </si>
-  <si>
-    <t>El corazón siempre guarda un rincón de esperanza</t>
+    <t>Siempre（原形） | 比较级: más Siempre | 最高级: lo más Siempre</t>
+  </si>
+  <si>
+    <t>他心灵总是珍藏着一隅希望。</t>
+  </si>
+  <si>
+    <t>El corazón siempre guarda un rincón de esperanza.</t>
   </si>
   <si>
     <t>频率副词，用于句中</t>
@@ -624,16 +606,13 @@
     <t>Nunca</t>
   </si>
   <si>
-    <t>从不</t>
-  </si>
-  <si>
-    <t>Nunca（原形）</t>
-  </si>
-  <si>
-    <t>因为我们从不知道，黎明将于何时决心再次渲染天际</t>
-  </si>
-  <si>
-    <t>porque nunca sabemos cuando el amanecer decidira pintar el cielo de nuevo</t>
+    <t>Nunca（原形） | 比较级: más Nunca | 最高级: lo más Nunca</t>
+  </si>
+  <si>
+    <t>因为我们从不知道，黎明将于何时决心再次渲染天际。</t>
+  </si>
+  <si>
+    <t>Él porque nunca sabemos cuando el amanecer decidira pintar el cielo de nuevo.</t>
   </si>
   <si>
     <t>否定副词，用于句中</t>
@@ -645,13 +624,13 @@
     <t>稍后</t>
   </si>
   <si>
-    <t>Luego（原形）</t>
-  </si>
-  <si>
-    <t>而后，当我们终于迈出脚步时</t>
-  </si>
-  <si>
-    <t>Luego, cuando al fin demos el paso</t>
+    <t>Luego（原形） | 比较级: más Luego | 最高级: lo más Luego</t>
+  </si>
+  <si>
+    <t>而后，当我们终于迈出脚步时。</t>
+  </si>
+  <si>
+    <t>Él Luego, cuando al fin demos el paso.</t>
   </si>
   <si>
     <t>时间副词，用于句首</t>
@@ -663,13 +642,13 @@
     <t>已经</t>
   </si>
   <si>
-    <t>Ya（原形）</t>
-  </si>
-  <si>
-    <t>我们已抵达人生的十字路口</t>
-  </si>
-  <si>
-    <t>Ya hemos llegado al cruce de caminos</t>
+    <t>Ya（原形） | 比较级: más Ya | 最高级: lo más Ya</t>
+  </si>
+  <si>
+    <t>我们已抵达人生的十字路口。</t>
+  </si>
+  <si>
+    <t>Él Ya hemos llegado al cruce de caminos.</t>
   </si>
   <si>
     <t>时间副词，用于句中</t>
@@ -678,19 +657,13 @@
     <t>Todavia</t>
   </si>
   <si>
-    <t>仍然</t>
-  </si>
-  <si>
-    <t>Todavía（原形）</t>
-  </si>
-  <si>
-    <t>却仍然彷徨于前进的方向</t>
-  </si>
-  <si>
-    <t>pero todavía dudamos sobre la dirección</t>
-  </si>
-  <si>
-    <t>副词，用于句中，表仍然</t>
+    <t>Todavía（原形） | 比较级: más Todavia | 最高级: lo más Todavia</t>
+  </si>
+  <si>
+    <t>他却仍然彷徨于前进的方向。</t>
+  </si>
+  <si>
+    <t>Él pero todavía dudamos sobre la dirección.</t>
   </si>
   <si>
     <t>Ahora</t>
@@ -699,16 +672,13 @@
     <t>现在</t>
   </si>
   <si>
-    <t>Ahora（原形）</t>
-  </si>
-  <si>
-    <t>但唯有此刻，我们才真正觉醒和存在</t>
-  </si>
-  <si>
-    <t>pero solo ahora despertamos y existimos de verdad</t>
-  </si>
-  <si>
-    <t>时间副词，用于句首/句末</t>
+    <t>Ahora（原形） | 比较级: más Ahora | 最高级: lo más Ahora</t>
+  </si>
+  <si>
+    <t>但唯有此刻，我们才真正觉醒和存在。</t>
+  </si>
+  <si>
+    <t>Él pero solo ahora despertamos y existimos de verdad.</t>
   </si>
   <si>
     <t>Antes</t>
@@ -717,16 +687,13 @@
     <t>以前</t>
   </si>
   <si>
-    <t>Antes（原形）</t>
-  </si>
-  <si>
-    <t>以前我们沉睡于往昔的旧梦</t>
-  </si>
-  <si>
-    <t>Antes dormiamos en el sueno del pasado</t>
-  </si>
-  <si>
-    <t>时间副词，用于句首</t>
+    <t>Antes（原形） | 比较级: más Antes | 最高级: lo más Antes</t>
+  </si>
+  <si>
+    <t>以前我们沉睡于往昔的旧梦。</t>
+  </si>
+  <si>
+    <t>Él Antes dormiamos en el sueno del pasado.</t>
   </si>
   <si>
     <t>Después</t>
@@ -735,16 +702,13 @@
     <t>之后</t>
   </si>
   <si>
-    <t>Después（原形）</t>
-  </si>
-  <si>
-    <t>以后我们将追寻于未来的蓝图</t>
-  </si>
-  <si>
-    <t>después buscaremos en el proyecto del futuro</t>
-  </si>
-  <si>
-    <t>时间副词，用于句首/句末</t>
+    <t>Después（原形） | 比较级: más Después | 最高级: lo más Después</t>
+  </si>
+  <si>
+    <t>以后我们将追寻于未来的蓝图。</t>
+  </si>
+  <si>
+    <t>Él después buscaremos en el proyecto del futuro.</t>
   </si>
 </sst>
 </file>
@@ -760,16 +724,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -823,19 +787,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -872,7 +836,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="MtcYmY">
+        <xdr:cNvPr id="2" name="Picture 2" descr="XesNed">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
@@ -1200,11 +1164,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A5CBE7-7242-41DC-821D-78DCC113BFD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88F77A6-CFD3-4865-B1BC-AD5051B21FF5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1236,782 +1200,802 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>233</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>239</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" t="s">
+        <v>226</v>
+      </c>
+      <c r="E41" t="s">
+        <v>227</v>
+      </c>
+      <c r="F41" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
